--- a/wellness_forms/026_family_therapy_intake_form--wellness_forms.xlsx
+++ b/wellness_forms/026_family_therapy_intake_form--wellness_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'single',_'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Single', 'value': 'single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'married',_'value':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Married', 'value': 'married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'divorced',_'value':_'divorced'}</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Divorced', 'value': 'divorced'}</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'in_a_domestic_partnership',_'value':_'domestic_partnership'}</t>
+          <t>in_a_domestic_partnership</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'In a Domestic Partnership', 'value': 'domestic_partnership'}</t>
+          <t>In a Domestic Partnership</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'1-2',_'value':_'1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '1-2', 'value': '1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'3-4',_'value':_'3-4'}</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '3-4', 'value': '3-4'}</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'5_or_more',_'value':_'5_or_more'}</t>
+          <t>5_or_more</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '5 or More', 'value': '5_or_more'}</t>
+          <t>5 or More</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Male', 'value': 'male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Female', 'value': 'female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Daily', 'value': 'daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'bi-weekly',_'value':_'bi_weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Bi-Weekly', 'value': 'bi_weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_weeks',_'value':_'1-2_weeks'}</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '1-2 weeks', 'value': '1-2_weeks'}</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'2-4_weeks',_'value':_'2-4_weeks'}</t>
+          <t>2-4_weeks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '2-4 weeks', 'value': '2-4_weeks'}</t>
+          <t>2-4 weeks</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'1-3_months',_'value':_'1-3_months'}</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': '1-3 months', 'value': '1-3_months'}</t>
+          <t>1-3 months</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'insurance',_'value':_'insurance'}</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Insurance', 'value': 'insurance'}</t>
+          <t>Insurance</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'self-pay',_'value':_'self_pay'}</t>
+          <t>self-pay</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Self-Pay', 'value': 'self_pay'}</t>
+          <t>Self-Pay</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'available',_'value':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Available', 'value': 'available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_available',_'value':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not Available', 'value': 'not_available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
